--- a/1일차 설명.xlsx
+++ b/1일차 설명.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\public\mbc\AGI_2026_09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7F513F1-E5DD-464F-985E-299E4F1C8265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4C2414-6D4E-477E-971D-1D3FA4553A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{233225A8-6C75-4D88-AC62-225E05A6B6E9}"/>
   </bookViews>
@@ -401,9 +401,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>275186</xdr:colOff>
+      <xdr:colOff>271376</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>27679</xdr:rowOff>
+      <xdr:rowOff>31489</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -762,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="26.25" customHeight="1">
+    <row r="43" spans="2:3" ht="30">
       <c r="B43" s="3" t="s">
         <v>3</v>
       </c>
